--- a/src/test/resources/testdata/demoqa-login-data-simple.xlsx
+++ b/src/test/resources/testdata/demoqa-login-data-simple.xlsx
@@ -3,24 +3,25 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Capgemini Training\MCP\src\test\resources\testdata\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CC9984-E49C-4900-89C0-F3C6A3201CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{B0B8D37D-91CC-4DE3-AD25-BD64A2324855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <oleSize ref="A1"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>username</t>
   </si>
@@ -62,49 +63,21 @@
   </si>
   <si>
     <t>wrongpass5</t>
-  </si>
-  <si>
-    <t>wronguser6</t>
-  </si>
-  <si>
-    <t>wrongpass6</t>
-  </si>
-  <si>
-    <t>wronguser7</t>
-  </si>
-  <si>
-    <t>wrongpass7</t>
-  </si>
-  <si>
-    <t>wronguser8</t>
-  </si>
-  <si>
-    <t>wrongpass8</t>
-  </si>
-  <si>
-    <t>wronguser9</t>
-  </si>
-  <si>
-    <t>wrongpass9</t>
-  </si>
-  <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>wronguser10</t>
-  </si>
-  <si>
-    <t>wrongpass10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -127,8 +100,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -147,9 +121,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -187,7 +161,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -293,7 +267,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -435,7 +409,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -444,13 +418,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.796875" customWidth="1"/>
-    <col min="2" max="2" width="17.265625" customWidth="1"/>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="2" max="2" width="17.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -461,7 +435,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -472,7 +446,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -483,7 +457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -494,7 +468,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -505,8 +479,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B6" t="s">
@@ -516,61 +490,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>22</v>
-      </c>
-    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/testdata/demoqa-login-data-simple.xlsx
+++ b/src/test/resources/testdata/demoqa-login-data-simple.xlsx
@@ -3,15 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\MCP\MCP\src\test\resources\testdata\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{B0B8D37D-91CC-4DE3-AD25-BD64A2324855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2616" yWindow="2616" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
@@ -69,7 +73,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -121,9 +125,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -161,7 +165,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -267,7 +271,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -409,7 +413,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -417,14 +421,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="15.77734375" customWidth="1"/>
     <col min="2" max="2" width="17.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -435,7 +439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -446,7 +450,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -457,7 +461,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -468,7 +472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -479,7 +483,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -490,11 +494,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
